--- a/Rapport_Reservations.xlsx
+++ b/Rapport_Reservations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>ID</t>
   </si>
@@ -29,28 +29,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>EN_ATTENTE</t>
-  </si>
-  <si>
-    <t>2026-02-22T15:10:07</t>
-  </si>
-  <si>
-    <t>2026-02-22T13:01:12</t>
-  </si>
-  <si>
-    <t>2026-02-22T11:35:06</t>
-  </si>
-  <si>
-    <t>2026-02-21T21:40:41</t>
-  </si>
-  <si>
-    <t>2026-02-21T21:37:43</t>
-  </si>
-  <si>
     <t>CONFIRMEE</t>
   </si>
   <si>
-    <t>2025-02-20T07:03</t>
+    <t>2026-02-26T21:02</t>
+  </si>
+  <si>
+    <t>2026-02-26T20:43:26</t>
   </si>
 </sst>
 </file>
@@ -112,13 +97,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="3.26953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="3.03125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="8.69140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="6.66015625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="12.68359375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="20.24609375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -141,13 +126,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
-        <v>30.0</v>
+        <v>2.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>5</v>
@@ -158,13 +143,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
-        <v>28.0</v>
+        <v>1.0</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>5</v>
@@ -173,74 +158,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n" s="0">
-        <v>26.0</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="B5" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n" s="0">
-        <v>23.0</v>
-      </c>
-      <c r="B6" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="B7" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="C7" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
